--- a/RQ_folder_MAIN/clustered_issues_FINAL.xlsx
+++ b/RQ_folder_MAIN/clustered_issues_FINAL.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ehsan_shahmi\ResearchPapers\Security_Hardening_Nov25\RQ_folder_MAIN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1C46BB0-EE3F-4862-A870-A63359EC7F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA01B4B6-57AC-4AEB-BA13-49D49B993277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="sampled_security_issues_v2" sheetId="3" r:id="rId2"/>
+    <sheet name="sampled_security_issues" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1047" uniqueCount="565">
   <si>
     <t>cwe_list</t>
   </si>
@@ -276,9 +279,6 @@
   </si>
   <si>
     <t>CWE-460</t>
-  </si>
-  <si>
-    <t>['userfaultfd: hugetlbfs: remove superfluous page unlock in VM_SHARED case\n\nhuge_add_to_page_cache-&gt;add_to_page_cache implicitly unlocks the page\nbefore returning in case of errors.\n\nThe error returned was -EEXIST by running UFFDIO_COPY on a non-hole\noffset of a VM_SHARED hugetlbfs mapping.  It was an userland bug that\ntriggered it and the kernel must cope with it returning -EEXIST from\nioctl(UFFDIO_COPY) as expected.\n\n  page dumped because: VM_BUG_ON_PAGE(!PageLocked(page))\n  kernel BUG at mm/filemap.c:964!\n  invalid opcode: 0000 [#1] SMP\n  CPU: 1 PID: 22582 Comm: qemu-system-x86 Not tainted 4.11.11-300.fc26.x86_64 #1\n  RIP: unlock_page+0x4a/0x50\n  Call Trace:\n    hugetlb_mcopy_atomic_pte+0xc0/0x320\n    mcopy_atomic+0x96f/0xbe0\n    userfaultfd_ioctl+0x218/0xe90\n    do_vfs_ioctl+0xa5/0x600\n    SyS_ioctl+0x79/0x90\n    entry_SYSCALL_64_fastpath+0x1a/0xa9\n\nLink: http://lkml.kernel.org/r/20170802165145.22628-2-aarcange@redhat.com\nSigned-off-by: Andrea Arcangeli &lt;aarcange@redhat.com&gt;\nTested-by: Maxime Coquelin &lt;maxime.coquelin@redhat.com&gt;\nReviewed-by: Mike Kravetz &lt;mike.kravetz@oracle.com&gt;\nCc: "Dr. David Alan Gilbert" &lt;dgilbert@redhat.com&gt;\nCc: Mike Rapoport &lt;rppt@linux.vnet.ibm.com&gt;\nCc: Alexey Perevalov &lt;a.perevalov@samsung.com&gt;\nSigned-off-by: Andrew Morton &lt;akpm@linux-foundation.org&gt;\nSigned-off-by: Linus Torvalds &lt;torvalds@linux-foundation.org&gt;']</t>
   </si>
   <si>
     <t>CWE-476</t>
@@ -589,9 +589,6 @@
     <t>Interpretation Conflict</t>
   </si>
   <si>
-    <t>Improper Cleanup on Thrown Exception</t>
-  </si>
-  <si>
     <t>Insertion of Sensitive Information into Log File</t>
   </si>
   <si>
@@ -599,6 +596,1167 @@
   </si>
   <si>
     <t>Reachable Assertion</t>
+  </si>
+  <si>
+    <t>CWE_Type</t>
+  </si>
+  <si>
+    <t>Filename</t>
+  </si>
+  <si>
+    <t>CWE-119_issue_105.txt</t>
+  </si>
+  <si>
+    <t>CWE-119_issue_107.txt</t>
+  </si>
+  <si>
+    <t>CWE-119_issue_141.txt</t>
+  </si>
+  <si>
+    <t>CWE-119_issue_149.txt</t>
+  </si>
+  <si>
+    <t>CWE-119_issue_173.txt</t>
+  </si>
+  <si>
+    <t>CWE-119_issue_184.txt</t>
+  </si>
+  <si>
+    <t>CWE-119_issue_196.txt</t>
+  </si>
+  <si>
+    <t>CWE-119_issue_24.txt</t>
+  </si>
+  <si>
+    <t>CWE-119_issue_33.txt</t>
+  </si>
+  <si>
+    <t>CWE-119_issue_40.txt</t>
+  </si>
+  <si>
+    <t>CWE-119_issue_47.txt</t>
+  </si>
+  <si>
+    <t>CWE-119_issue_8.txt</t>
+  </si>
+  <si>
+    <t>CWE-120_issue_2.txt</t>
+  </si>
+  <si>
+    <t>CWE-122_issue_1.txt</t>
+  </si>
+  <si>
+    <t>CWE-125_issue_101.txt</t>
+  </si>
+  <si>
+    <t>CWE-125_issue_24.txt</t>
+  </si>
+  <si>
+    <t>CWE-125_issue_31.txt</t>
+  </si>
+  <si>
+    <t>CWE-125_issue_46.txt</t>
+  </si>
+  <si>
+    <t>CWE-125_issue_52.txt</t>
+  </si>
+  <si>
+    <t>CWE-125_issue_63.txt</t>
+  </si>
+  <si>
+    <t>CWE-125_issue_70.txt</t>
+  </si>
+  <si>
+    <t>CWE-125_issue_86.txt</t>
+  </si>
+  <si>
+    <t>CWE-125_issue_93.txt</t>
+  </si>
+  <si>
+    <t>CWE-125_issue_94.txt</t>
+  </si>
+  <si>
+    <t>CWE-1284_issue_2.txt</t>
+  </si>
+  <si>
+    <t>CWE-129_issue_3.txt</t>
+  </si>
+  <si>
+    <t>CWE-16_issue_1.txt</t>
+  </si>
+  <si>
+    <t>CWE-17_issue_16.txt</t>
+  </si>
+  <si>
+    <t>CWE-17_issue_19.txt</t>
+  </si>
+  <si>
+    <t>CWE-189_issue_25.txt</t>
+  </si>
+  <si>
+    <t>CWE-189_issue_57.txt</t>
+  </si>
+  <si>
+    <t>CWE-189_issue_60.txt</t>
+  </si>
+  <si>
+    <t>CWE-19_issue_1.txt</t>
+  </si>
+  <si>
+    <t>CWE-19_issue_20.txt</t>
+  </si>
+  <si>
+    <t>CWE-190_issue_12.txt</t>
+  </si>
+  <si>
+    <t>CWE-190_issue_16.txt</t>
+  </si>
+  <si>
+    <t>CWE-190_issue_31.txt</t>
+  </si>
+  <si>
+    <t>CWE-190_issue_50.txt</t>
+  </si>
+  <si>
+    <t>CWE-191_issue_1.txt</t>
+  </si>
+  <si>
+    <t>CWE-193_issue_1.txt</t>
+  </si>
+  <si>
+    <t>CWE-20_issue_100.txt</t>
+  </si>
+  <si>
+    <t>CWE-20_issue_103.txt</t>
+  </si>
+  <si>
+    <t>CWE-20_issue_110.txt</t>
+  </si>
+  <si>
+    <t>CWE-20_issue_128.txt</t>
+  </si>
+  <si>
+    <t>CWE-20_issue_137.txt</t>
+  </si>
+  <si>
+    <t>CWE-20_issue_147.txt</t>
+  </si>
+  <si>
+    <t>CWE-20_issue_149.txt</t>
+  </si>
+  <si>
+    <t>CWE-20_issue_19.txt</t>
+  </si>
+  <si>
+    <t>CWE-20_issue_22.txt</t>
+  </si>
+  <si>
+    <t>CWE-20_issue_27.txt</t>
+  </si>
+  <si>
+    <t>CWE-20_issue_3.txt</t>
+  </si>
+  <si>
+    <t>CWE-20_issue_41.txt</t>
+  </si>
+  <si>
+    <t>CWE-20_issue_55.txt</t>
+  </si>
+  <si>
+    <t>CWE-20_issue_69.txt</t>
+  </si>
+  <si>
+    <t>CWE-20_issue_77.txt</t>
+  </si>
+  <si>
+    <t>CWE-200_issue_16.txt</t>
+  </si>
+  <si>
+    <t>CWE-200_issue_35.txt</t>
+  </si>
+  <si>
+    <t>CWE-200_issue_45.txt</t>
+  </si>
+  <si>
+    <t>CWE-203_issue_2.txt</t>
+  </si>
+  <si>
+    <t>CWE-203_issue_4.txt</t>
+  </si>
+  <si>
+    <t>CWE-22_issue_2.txt</t>
+  </si>
+  <si>
+    <t>CWE-254_issue_2.txt</t>
+  </si>
+  <si>
+    <t>CWE-264_issue_31.txt</t>
+  </si>
+  <si>
+    <t>CWE-264_issue_5.txt</t>
+  </si>
+  <si>
+    <t>CWE-264_issue_70.txt</t>
+  </si>
+  <si>
+    <t>CWE-269_issue_4.txt</t>
+  </si>
+  <si>
+    <t>CWE-276_issue_2.txt</t>
+  </si>
+  <si>
+    <t>CWE-284_issue_11.txt</t>
+  </si>
+  <si>
+    <t>CWE-285_issue_15.txt</t>
+  </si>
+  <si>
+    <t>CWE-287_issue_3.txt</t>
+  </si>
+  <si>
+    <t>CWE-310_issue_1.txt</t>
+  </si>
+  <si>
+    <t>CWE-319_issue_2.txt</t>
+  </si>
+  <si>
+    <t>CWE-319_issue_3.txt</t>
+  </si>
+  <si>
+    <t>CWE-326_issue_1.txt</t>
+  </si>
+  <si>
+    <t>CWE-358_issue_1.txt</t>
+  </si>
+  <si>
+    <t>CWE-362_issue_104.txt</t>
+  </si>
+  <si>
+    <t>CWE-362_issue_137.txt</t>
+  </si>
+  <si>
+    <t>CWE-362_issue_152.txt</t>
+  </si>
+  <si>
+    <t>CWE-362_issue_153.txt</t>
+  </si>
+  <si>
+    <t>CWE-362_issue_183.txt</t>
+  </si>
+  <si>
+    <t>CWE-362_issue_184.txt</t>
+  </si>
+  <si>
+    <t>CWE-362_issue_221.txt</t>
+  </si>
+  <si>
+    <t>CWE-362_issue_223.txt</t>
+  </si>
+  <si>
+    <t>CWE-362_issue_230.txt</t>
+  </si>
+  <si>
+    <t>CWE-362_issue_26.txt</t>
+  </si>
+  <si>
+    <t>CWE-362_issue_45.txt</t>
+  </si>
+  <si>
+    <t>CWE-362_issue_6.txt</t>
+  </si>
+  <si>
+    <t>CWE-362_issue_63.txt</t>
+  </si>
+  <si>
+    <t>CWE-362_issue_73.txt</t>
+  </si>
+  <si>
+    <t>CWE-362_issue_84.txt</t>
+  </si>
+  <si>
+    <t>CWE-367_issue_5.txt</t>
+  </si>
+  <si>
+    <t>CWE-369_issue_1.txt</t>
+  </si>
+  <si>
+    <t>CWE-369_issue_2.txt</t>
+  </si>
+  <si>
+    <t>CWE-388_issue_2.txt</t>
+  </si>
+  <si>
+    <t>CWE-399_issue_33.txt</t>
+  </si>
+  <si>
+    <t>CWE-399_issue_51.txt</t>
+  </si>
+  <si>
+    <t>CWE-399_issue_57.txt</t>
+  </si>
+  <si>
+    <t>CWE-400_issue_32.txt</t>
+  </si>
+  <si>
+    <t>CWE-400_issue_42.txt</t>
+  </si>
+  <si>
+    <t>CWE-400_issue_63.txt</t>
+  </si>
+  <si>
+    <t>CWE-400_issue_64.txt</t>
+  </si>
+  <si>
+    <t>CWE-400_issue_77.txt</t>
+  </si>
+  <si>
+    <t>CWE-400_issue_80.txt</t>
+  </si>
+  <si>
+    <t>CWE-400_issue_84.txt</t>
+  </si>
+  <si>
+    <t>CWE-400_issue_94.txt</t>
+  </si>
+  <si>
+    <t>CWE-401_issue_36.txt</t>
+  </si>
+  <si>
+    <t>CWE-404_issue_1.txt</t>
+  </si>
+  <si>
+    <t>CWE-415_issue_10.txt</t>
+  </si>
+  <si>
+    <t>CWE-415_issue_34.txt</t>
+  </si>
+  <si>
+    <t>CWE-415_issue_35.txt</t>
+  </si>
+  <si>
+    <t>CWE-415_issue_37.txt</t>
+  </si>
+  <si>
+    <t>CWE-415_issue_43.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_123.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_128.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_139.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_152.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_153.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_191.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_197.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_203.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_239.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_277.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_289.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_293.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_323.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_328.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_362.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_39.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_391.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_404.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_418.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_425.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_466.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_473.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_485.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_49.txt</t>
+  </si>
+  <si>
+    <t>CWE-436_issue_1.txt</t>
+  </si>
+  <si>
+    <t>CWE-460_issue_1.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_138.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_142.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_158.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_162.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_17.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_170.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_19.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_20.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_203.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_21.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_216.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_231.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_264.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_283.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_343.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_368.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_37.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_378.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_389.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_411.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_440.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_459.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_491.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_504.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_54.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_77.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_87.txt</t>
+  </si>
+  <si>
+    <t>CWE-532_issue_1.txt</t>
+  </si>
+  <si>
+    <t>CWE-59_issue_1.txt</t>
+  </si>
+  <si>
+    <t>CWE-617_issue_1.txt</t>
+  </si>
+  <si>
+    <t>CWE-665_issue_4.txt</t>
+  </si>
+  <si>
+    <t>CWE-667_issue_2.txt</t>
+  </si>
+  <si>
+    <t>CWE-667_issue_3.txt</t>
+  </si>
+  <si>
+    <t>CWE-667_issue_4.txt</t>
+  </si>
+  <si>
+    <t>CWE-674_issue_4.txt</t>
+  </si>
+  <si>
+    <t>CWE-681_issue_2.txt</t>
+  </si>
+  <si>
+    <t>CWE-682_issue_1.txt</t>
+  </si>
+  <si>
+    <t>CWE-704_issue_2.txt</t>
+  </si>
+  <si>
+    <t>CWE-732_issue_3.txt</t>
+  </si>
+  <si>
+    <t>CWE-754_issue_2.txt</t>
+  </si>
+  <si>
+    <t>CWE-755_issue_1.txt</t>
+  </si>
+  <si>
+    <t>CWE-763_issue_3.txt</t>
+  </si>
+  <si>
+    <t>CWE-772_issue_1.txt</t>
+  </si>
+  <si>
+    <t>CWE-787_issue_109.txt</t>
+  </si>
+  <si>
+    <t>CWE-787_issue_116.txt</t>
+  </si>
+  <si>
+    <t>CWE-787_issue_13.txt</t>
+  </si>
+  <si>
+    <t>CWE-787_issue_147.txt</t>
+  </si>
+  <si>
+    <t>CWE-787_issue_34.txt</t>
+  </si>
+  <si>
+    <t>CWE-787_issue_65.txt</t>
+  </si>
+  <si>
+    <t>CWE-787_issue_69.txt</t>
+  </si>
+  <si>
+    <t>CWE-787_issue_71.txt</t>
+  </si>
+  <si>
+    <t>CWE-787_issue_77.txt</t>
+  </si>
+  <si>
+    <t>CWE-787_issue_8.txt</t>
+  </si>
+  <si>
+    <t>CWE-787_issue_88.txt</t>
+  </si>
+  <si>
+    <t>CWE-787_issue_96.txt</t>
+  </si>
+  <si>
+    <t>CWE-824_issue_2.txt</t>
+  </si>
+  <si>
+    <t>CWE-835_issue_2.txt</t>
+  </si>
+  <si>
+    <t>CWE-843_issue_1.txt</t>
+  </si>
+  <si>
+    <t>CWE-862_issue_2.txt</t>
+  </si>
+  <si>
+    <t>CWE-863_issue_2.txt</t>
+  </si>
+  <si>
+    <t>CWE-908_issue_6.txt</t>
+  </si>
+  <si>
+    <t>CWE-909_issue_1.txt</t>
+  </si>
+  <si>
+    <t>mutant correct or not</t>
+  </si>
+  <si>
+    <t>cweval file</t>
+  </si>
+  <si>
+    <t>Improper Restriction of Operations within the Bounds of a Memory Buffer</t>
+  </si>
+  <si>
+    <t>020_0</t>
+  </si>
+  <si>
+    <t>classic buffer overflow</t>
+  </si>
+  <si>
+    <t>no change</t>
+  </si>
+  <si>
+    <t>022_0</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>326_0</t>
+  </si>
+  <si>
+    <t>326_1</t>
+  </si>
+  <si>
+    <t>Incorrect Permission Assignment for Critical Resource</t>
+  </si>
+  <si>
+    <t>732_2</t>
+  </si>
+  <si>
+    <t>CWE-119_issue_1.txt</t>
+  </si>
+  <si>
+    <t>Out-of-bounds Read</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>final unique count</t>
+  </si>
+  <si>
+    <t>CWE-119_issue_131.txt</t>
+  </si>
+  <si>
+    <t>CWE-119_issue_137.txt</t>
+  </si>
+  <si>
+    <t>CWE-119_issue_146.txt</t>
+  </si>
+  <si>
+    <t>CWE-119_issue_207.txt</t>
+  </si>
+  <si>
+    <t>CWE-119_issue_35.txt</t>
+  </si>
+  <si>
+    <t>CWE-119_issue_51.txt</t>
+  </si>
+  <si>
+    <t>CWE-119_issue_56.txt</t>
+  </si>
+  <si>
+    <t>CWE-119_issue_59.txt</t>
+  </si>
+  <si>
+    <t>CWE-119_issue_65.txt</t>
+  </si>
+  <si>
+    <t>CWE-119_issue_80.txt</t>
+  </si>
+  <si>
+    <t>CWE-119_issue_83.txt</t>
+  </si>
+  <si>
+    <t>CWE-120_issue_3.txt</t>
+  </si>
+  <si>
+    <t>CWE-120_issue_8.txt</t>
+  </si>
+  <si>
+    <t>CWE-125_issue_2.txt</t>
+  </si>
+  <si>
+    <t>CWE-125_issue_27.txt</t>
+  </si>
+  <si>
+    <t>CWE-1284_issue_1.txt</t>
+  </si>
+  <si>
+    <t>CWE-129_issue_2.txt</t>
+  </si>
+  <si>
+    <t>CWE-17_issue_3.txt</t>
+  </si>
+  <si>
+    <t>CWE-189_issue_15.txt</t>
+  </si>
+  <si>
+    <t>CWE-189_issue_21.txt</t>
+  </si>
+  <si>
+    <t>CWE-189_issue_23.txt</t>
+  </si>
+  <si>
+    <t>CWE-189_issue_30.txt</t>
+  </si>
+  <si>
+    <t>CWE-19_issue_12.txt</t>
+  </si>
+  <si>
+    <t>CWE-19_issue_15.txt</t>
+  </si>
+  <si>
+    <t>CWE-190_issue_46.txt</t>
+  </si>
+  <si>
+    <t>CWE-190_issue_52.txt</t>
+  </si>
+  <si>
+    <t>CWE-190_issue_56.txt</t>
+  </si>
+  <si>
+    <t>CWE-190_issue_58.txt</t>
+  </si>
+  <si>
+    <t>CWE-20_issue_131.txt</t>
+  </si>
+  <si>
+    <t>CWE-20_issue_2.txt</t>
+  </si>
+  <si>
+    <t>CWE-20_issue_47.txt</t>
+  </si>
+  <si>
+    <t>CWE-20_issue_48.txt</t>
+  </si>
+  <si>
+    <t>CWE-20_issue_50.txt</t>
+  </si>
+  <si>
+    <t>CWE-20_issue_70.txt</t>
+  </si>
+  <si>
+    <t>CWE-20_issue_96.txt</t>
+  </si>
+  <si>
+    <t>CWE-200_issue_10.txt</t>
+  </si>
+  <si>
+    <t>CWE-200_issue_14.txt</t>
+  </si>
+  <si>
+    <t>CWE-200_issue_22.txt</t>
+  </si>
+  <si>
+    <t>CWE-200_issue_31.txt</t>
+  </si>
+  <si>
+    <t>CWE-200_issue_39.txt</t>
+  </si>
+  <si>
+    <t>CWE-200_issue_48.txt</t>
+  </si>
+  <si>
+    <t>CWE-200_issue_60.txt</t>
+  </si>
+  <si>
+    <t>CWE-22_issue_1.txt</t>
+  </si>
+  <si>
+    <t>CWE-254_issue_1.txt</t>
+  </si>
+  <si>
+    <t>CWE-264_issue_42.txt</t>
+  </si>
+  <si>
+    <t>CWE-264_issue_56.txt</t>
+  </si>
+  <si>
+    <t>CWE-264_issue_8.txt</t>
+  </si>
+  <si>
+    <t>CWE-269_issue_2.txt</t>
+  </si>
+  <si>
+    <t>CWE-276_issue_3.txt</t>
+  </si>
+  <si>
+    <t>CWE-284_issue_5.txt</t>
+  </si>
+  <si>
+    <t>CWE-285_issue_24.txt</t>
+  </si>
+  <si>
+    <t>CWE-285_issue_6.txt</t>
+  </si>
+  <si>
+    <t>CWE-310_issue_10.txt</t>
+  </si>
+  <si>
+    <t>CWE-310_issue_7.txt</t>
+  </si>
+  <si>
+    <t>CWE-319_issue_1.txt</t>
+  </si>
+  <si>
+    <t>CWE-326_issue_2.txt</t>
+  </si>
+  <si>
+    <t>CWE-362_issue_109.txt</t>
+  </si>
+  <si>
+    <t>CWE-362_issue_174.txt</t>
+  </si>
+  <si>
+    <t>CWE-362_issue_176.txt</t>
+  </si>
+  <si>
+    <t>CWE-362_issue_179.txt</t>
+  </si>
+  <si>
+    <t>CWE-362_issue_180.txt</t>
+  </si>
+  <si>
+    <t>CWE-362_issue_231.txt</t>
+  </si>
+  <si>
+    <t>CWE-362_issue_4.txt</t>
+  </si>
+  <si>
+    <t>CWE-362_issue_43.txt</t>
+  </si>
+  <si>
+    <t>CWE-362_issue_46.txt</t>
+  </si>
+  <si>
+    <t>CWE-362_issue_58.txt</t>
+  </si>
+  <si>
+    <t>CWE-362_issue_59.txt</t>
+  </si>
+  <si>
+    <t>CWE-362_issue_92.txt</t>
+  </si>
+  <si>
+    <t>CWE-362_issue_93.txt</t>
+  </si>
+  <si>
+    <t>CWE-367_issue_11.txt</t>
+  </si>
+  <si>
+    <t>CWE-367_issue_3.txt</t>
+  </si>
+  <si>
+    <t>CWE-369_issue_3.txt</t>
+  </si>
+  <si>
+    <t>CWE-388_issue_4.txt</t>
+  </si>
+  <si>
+    <t>CWE-399_issue_17.txt</t>
+  </si>
+  <si>
+    <t>CWE-399_issue_25.txt</t>
+  </si>
+  <si>
+    <t>CWE-399_issue_3.txt</t>
+  </si>
+  <si>
+    <t>CWE-399_issue_43.txt</t>
+  </si>
+  <si>
+    <t>CWE-400_issue_14.txt</t>
+  </si>
+  <si>
+    <t>CWE-400_issue_44.txt</t>
+  </si>
+  <si>
+    <t>CWE-400_issue_54.txt</t>
+  </si>
+  <si>
+    <t>CWE-400_issue_73.txt</t>
+  </si>
+  <si>
+    <t>CWE-400_issue_82.txt</t>
+  </si>
+  <si>
+    <t>CWE-401_issue_12.txt</t>
+  </si>
+  <si>
+    <t>CWE-401_issue_32.txt</t>
+  </si>
+  <si>
+    <t>CWE-404_issue_5.txt</t>
+  </si>
+  <si>
+    <t>CWE-415_issue_17.txt</t>
+  </si>
+  <si>
+    <t>CWE-415_issue_29.txt</t>
+  </si>
+  <si>
+    <t>CWE-415_issue_30.txt</t>
+  </si>
+  <si>
+    <t>CWE-415_issue_36.txt</t>
+  </si>
+  <si>
+    <t>CWE-415_issue_39.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_108.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_115.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_13.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_130.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_147.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_150.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_179.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_18.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_187.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_193.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_215.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_236.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_256.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_270.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_275.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_33.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_337.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_338.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_346.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_348.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_35.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_350.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_429.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_43.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_433.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_438.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_449.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_60.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_7.txt</t>
+  </si>
+  <si>
+    <t>CWE-416_issue_86.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_103.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_104.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_133.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_168.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_175.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_189.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_238.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_263.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_27.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_270.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_282.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_284.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_29.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_293.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_31.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_317.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_330.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_332.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_335.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_342.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_348.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_353.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_390.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_420.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_428.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_448.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_456.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_46.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_49.txt</t>
+  </si>
+  <si>
+    <t>CWE-476_issue_62.txt</t>
+  </si>
+  <si>
+    <t>CWE-665_issue_2.txt</t>
+  </si>
+  <si>
+    <t>CWE-667_issue_5.txt</t>
+  </si>
+  <si>
+    <t>CWE-674_issue_5.txt</t>
+  </si>
+  <si>
+    <t>CWE-681_issue_1.txt</t>
+  </si>
+  <si>
+    <t>CWE-732_issue_1.txt</t>
+  </si>
+  <si>
+    <t>CWE-755_issue_2.txt</t>
+  </si>
+  <si>
+    <t>CWE-772_issue_3.txt</t>
+  </si>
+  <si>
+    <t>CWE-787_issue_100.txt</t>
+  </si>
+  <si>
+    <t>CWE-787_issue_103.txt</t>
+  </si>
+  <si>
+    <t>CWE-787_issue_108.txt</t>
+  </si>
+  <si>
+    <t>CWE-787_issue_123.txt</t>
+  </si>
+  <si>
+    <t>CWE-787_issue_15.txt</t>
+  </si>
+  <si>
+    <t>CWE-787_issue_4.txt</t>
+  </si>
+  <si>
+    <t>CWE-787_issue_46.txt</t>
+  </si>
+  <si>
+    <t>CWE-787_issue_64.txt</t>
+  </si>
+  <si>
+    <t>CWE-787_issue_94.txt</t>
+  </si>
+  <si>
+    <t>CWE-835_issue_1.txt</t>
+  </si>
+  <si>
+    <t>CWE-908_issue_3.txt</t>
+  </si>
+  <si>
+    <t>CWE-908_issue_4.txt</t>
   </si>
 </sst>
 </file>
@@ -628,7 +1786,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -656,6 +1814,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -687,7 +1863,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -730,6 +1906,28 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1033,12 +2231,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S71"/>
+  <dimension ref="A1:S70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.42578125" style="6" customWidth="1"/>
     <col min="2" max="2" width="9.140625" style="6"/>
-    <col min="3" max="3" width="16.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" style="1" customWidth="1"/>
     <col min="4" max="4" width="8.85546875" style="1" customWidth="1"/>
     <col min="5" max="5" width="9.140625" style="6"/>
     <col min="6" max="6" width="27" style="7" customWidth="1"/>
@@ -1051,7 +2249,7 @@
     <col min="20" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1059,28 +2257,31 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>138</v>
+      <c r="E1" s="2" t="s">
+        <v>395</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N1" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="S1" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="S1" s="9" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
@@ -1093,7 +2294,13 @@
       <c r="D2" s="1">
         <v>142</v>
       </c>
-      <c r="S2" s="10" t="s">
+      <c r="E2" s="4">
+        <v>207</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="S2" s="17" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1110,7 +2317,13 @@
       <c r="D3" s="1">
         <v>7</v>
       </c>
-      <c r="S3" s="10" t="s">
+      <c r="E3" s="4">
+        <v>10</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="S3" s="17" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1127,20 +2340,23 @@
       <c r="D4" s="1">
         <v>1</v>
       </c>
+      <c r="E4" s="4">
+        <v>1</v>
+      </c>
       <c r="F4" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N4" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="P4" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="O4" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>162</v>
-      </c>
       <c r="S4" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
@@ -1156,8 +2372,14 @@
       <c r="D5" s="1">
         <v>99</v>
       </c>
+      <c r="E5" s="4">
+        <v>105</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>393</v>
+      </c>
       <c r="S5" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
@@ -1173,8 +2395,11 @@
       <c r="D6" s="1">
         <v>2</v>
       </c>
+      <c r="E6" s="4">
+        <v>2</v>
+      </c>
       <c r="S6" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
@@ -1190,8 +2415,11 @@
       <c r="D7" s="1">
         <v>2</v>
       </c>
+      <c r="E7" s="4">
+        <v>3</v>
+      </c>
       <c r="S7" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
@@ -1207,10 +2435,13 @@
       <c r="D8" s="1">
         <v>1</v>
       </c>
+      <c r="E8" s="4">
+        <v>1</v>
+      </c>
       <c r="G8" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="S8" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="S8" s="17" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1227,8 +2458,11 @@
       <c r="D9" s="1">
         <v>9</v>
       </c>
+      <c r="E9" s="4">
+        <v>14</v>
+      </c>
       <c r="S9" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -1244,8 +2478,11 @@
       <c r="D10" s="1">
         <v>27</v>
       </c>
+      <c r="E10" s="4">
+        <v>61</v>
+      </c>
       <c r="S10" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
@@ -1261,8 +2498,11 @@
       <c r="D11" s="1">
         <v>8</v>
       </c>
+      <c r="E11" s="4">
+        <v>30</v>
+      </c>
       <c r="S11" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
@@ -1278,8 +2518,11 @@
       <c r="D12" s="1">
         <v>46</v>
       </c>
+      <c r="E12" s="4">
+        <v>58</v>
+      </c>
       <c r="S12" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -1295,20 +2538,23 @@
       <c r="D13" s="1">
         <v>1</v>
       </c>
+      <c r="E13" s="4">
+        <v>1</v>
+      </c>
       <c r="F13" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="N13" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="N13" s="4" t="s">
+      <c r="O13" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="O13" s="4" t="s">
-        <v>159</v>
-      </c>
       <c r="P13" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="S13" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
@@ -1324,20 +2570,23 @@
       <c r="D14" s="1">
         <v>1</v>
       </c>
+      <c r="E14" s="4">
+        <v>1</v>
+      </c>
       <c r="F14" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="O14" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="N14" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="O14" s="4" t="s">
-        <v>164</v>
-      </c>
       <c r="P14" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="S14" s="10" t="s">
-        <v>102</v>
+        <v>163</v>
+      </c>
+      <c r="S14" s="17" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
@@ -1353,20 +2602,23 @@
       <c r="D15" s="14">
         <v>72</v>
       </c>
+      <c r="E15" s="4">
+        <v>150</v>
+      </c>
       <c r="F15" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="N15" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="O15" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="N15" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="O15" s="4" t="s">
-        <v>166</v>
-      </c>
       <c r="P15" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
@@ -1382,8 +2634,11 @@
       <c r="D16" s="1">
         <v>50</v>
       </c>
+      <c r="E16" s="4">
+        <v>71</v>
+      </c>
       <c r="S16" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
@@ -1399,8 +2654,11 @@
       <c r="D17" s="1">
         <v>2</v>
       </c>
+      <c r="E17" s="4">
+        <v>4</v>
+      </c>
       <c r="S17" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="45" x14ac:dyDescent="0.25">
@@ -1416,11 +2674,14 @@
       <c r="D18" s="14">
         <v>1</v>
       </c>
+      <c r="E18" s="4">
+        <v>4</v>
+      </c>
       <c r="F18" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="N18" s="4" t="s">
         <v>167</v>
-      </c>
-      <c r="N18" s="4" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
@@ -1436,8 +2697,11 @@
       <c r="D19" s="1">
         <v>1</v>
       </c>
+      <c r="E19" s="4">
+        <v>1</v>
+      </c>
       <c r="G19" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
@@ -1453,6 +2717,9 @@
       <c r="D20" s="1">
         <v>36</v>
       </c>
+      <c r="E20" s="4">
+        <v>79</v>
+      </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
@@ -1467,6 +2734,9 @@
       <c r="D21" s="1">
         <v>10</v>
       </c>
+      <c r="E21" s="4">
+        <v>14</v>
+      </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
@@ -1481,6 +2751,9 @@
       <c r="D22" s="1">
         <v>2</v>
       </c>
+      <c r="E22" s="4">
+        <v>3</v>
+      </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
@@ -1495,6 +2768,9 @@
       <c r="D23" s="1">
         <v>7</v>
       </c>
+      <c r="E23" s="4">
+        <v>11</v>
+      </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
@@ -1509,8 +2785,11 @@
       <c r="D24" s="1">
         <v>1</v>
       </c>
+      <c r="E24" s="4">
+        <v>25</v>
+      </c>
       <c r="F24" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
@@ -1526,8 +2805,11 @@
       <c r="D25" s="1">
         <v>1</v>
       </c>
+      <c r="E25" s="4">
+        <v>3</v>
+      </c>
       <c r="F25" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
@@ -1543,6 +2825,9 @@
       <c r="D26" s="1">
         <v>4</v>
       </c>
+      <c r="E26" s="4">
+        <v>17</v>
+      </c>
     </row>
     <row r="27" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
@@ -1557,8 +2842,11 @@
       <c r="D27" s="1">
         <v>1</v>
       </c>
+      <c r="E27" s="4">
+        <v>2</v>
+      </c>
       <c r="F27" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="28" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -1574,8 +2862,11 @@
       <c r="D28" s="14">
         <v>1</v>
       </c>
+      <c r="E28" s="4">
+        <v>4</v>
+      </c>
       <c r="F28" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -1591,8 +2882,11 @@
       <c r="D29" s="1">
         <v>1</v>
       </c>
+      <c r="E29" s="4">
+        <v>1</v>
+      </c>
       <c r="F29" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
@@ -1608,6 +2902,9 @@
       <c r="D30" s="1">
         <v>145</v>
       </c>
+      <c r="E30" s="4">
+        <v>237</v>
+      </c>
     </row>
     <row r="31" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
@@ -1622,8 +2919,11 @@
       <c r="D31" s="1">
         <v>1</v>
       </c>
+      <c r="E31" s="4">
+        <v>13</v>
+      </c>
       <c r="F31" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
@@ -1639,6 +2939,9 @@
       <c r="D32" s="1">
         <v>2</v>
       </c>
+      <c r="E32" s="4">
+        <v>3</v>
+      </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
@@ -1653,6 +2956,9 @@
       <c r="D33" s="1">
         <v>2</v>
       </c>
+      <c r="E33" s="4">
+        <v>4</v>
+      </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
@@ -1667,6 +2973,9 @@
       <c r="D34" s="1">
         <v>41</v>
       </c>
+      <c r="E34" s="4">
+        <v>72</v>
+      </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
@@ -1681,6 +2990,9 @@
       <c r="D35" s="1">
         <v>12</v>
       </c>
+      <c r="E35" s="4">
+        <v>90</v>
+      </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
@@ -1695,6 +3007,9 @@
       <c r="D36" s="1">
         <v>36</v>
       </c>
+      <c r="E36" s="4">
+        <v>38</v>
+      </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
@@ -1709,6 +3024,9 @@
       <c r="D37" s="1">
         <v>3</v>
       </c>
+      <c r="E37" s="4">
+        <v>8</v>
+      </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
@@ -1723,6 +3041,9 @@
       <c r="D38" s="1">
         <v>39</v>
       </c>
+      <c r="E38" s="4">
+        <v>41</v>
+      </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
@@ -1737,6 +3058,9 @@
       <c r="D39" s="1">
         <v>368</v>
       </c>
+      <c r="E39" s="4">
+        <v>485</v>
+      </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
@@ -1751,47 +3075,56 @@
       <c r="D40" s="1">
         <v>1</v>
       </c>
+      <c r="E40" s="4">
+        <v>1</v>
+      </c>
       <c r="F40" s="7" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C41" s="1">
+        <v>507</v>
+      </c>
+      <c r="D41" s="1">
+        <v>403</v>
+      </c>
+      <c r="E41" s="4">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C42" s="1">
+        <v>1</v>
+      </c>
+      <c r="D42" s="1">
+        <v>1</v>
+      </c>
+      <c r="E42" s="4">
+        <v>1</v>
+      </c>
+      <c r="F42" s="7" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A41" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C41" s="1">
-        <v>1</v>
-      </c>
-      <c r="D41" s="1">
-        <v>1</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C42" s="1">
-        <v>507</v>
-      </c>
-      <c r="D42" s="1">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C43" s="1">
         <v>1</v>
@@ -1799,16 +3132,19 @@
       <c r="D43" s="1">
         <v>1</v>
       </c>
+      <c r="E43" s="4">
+        <v>1</v>
+      </c>
       <c r="F43" s="7" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C44" s="1">
         <v>1</v>
@@ -1816,159 +3152,192 @@
       <c r="D44" s="1">
         <v>1</v>
       </c>
+      <c r="E44" s="4">
+        <v>1</v>
+      </c>
       <c r="F44" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C45" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D45" s="1">
-        <v>1</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>179</v>
+        <v>5</v>
+      </c>
+      <c r="E45" s="4">
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C46" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D46" s="1">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="E46" s="4">
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C47" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D47" s="1">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="E47" s="4">
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C48" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D48" s="1">
+        <v>2</v>
+      </c>
+      <c r="E48" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C49" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C49" s="1">
+      <c r="D49" s="1">
+        <v>1</v>
+      </c>
+      <c r="E49" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C50" s="1">
         <v>2</v>
-      </c>
-      <c r="D49" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C50" s="1">
-        <v>1</v>
       </c>
       <c r="D50" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E50" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C51" s="1">
+        <v>3</v>
+      </c>
+      <c r="D51" s="14">
+        <v>1</v>
+      </c>
+      <c r="E51" s="4">
+        <v>3</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C52" s="1">
         <v>2</v>
       </c>
-      <c r="D51" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C52" s="1">
+      <c r="D52" s="1">
+        <v>2</v>
+      </c>
+      <c r="E52" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C53" s="1">
         <v>3</v>
       </c>
-      <c r="D52" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C53" s="1">
-        <v>2</v>
-      </c>
       <c r="D53" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="E53" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C54" s="1">
+        <v>4</v>
+      </c>
+      <c r="D54" s="1">
+        <v>4</v>
+      </c>
+      <c r="E54" s="4">
         <v>3</v>
       </c>
-      <c r="D54" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C55" s="1">
         <v>4</v>
@@ -1976,83 +3345,101 @@
       <c r="D55" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="6" t="s">
-        <v>110</v>
+      <c r="E55" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="5" t="s">
+        <v>111</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C56" s="1">
+        <v>150</v>
+      </c>
+      <c r="D56" s="1">
+        <v>112</v>
+      </c>
+      <c r="E56" s="4">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C57" s="1">
+        <v>2</v>
+      </c>
+      <c r="D57" s="1">
+        <v>2</v>
+      </c>
+      <c r="E57" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C58" s="1">
+        <v>9</v>
+      </c>
+      <c r="D58" s="1">
         <v>4</v>
       </c>
-      <c r="D56" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C57" s="1">
-        <v>150</v>
-      </c>
-      <c r="D57" s="1">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C58" s="1">
+      <c r="E58" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C59" s="1">
+        <v>1</v>
+      </c>
+      <c r="D59" s="1">
+        <v>1</v>
+      </c>
+      <c r="E59" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C60" s="1">
         <v>2</v>
       </c>
-      <c r="D58" s="1">
+      <c r="D60" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C59" s="1">
-        <v>9</v>
-      </c>
-      <c r="D59" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="C60" s="1">
-        <v>1</v>
-      </c>
-      <c r="D60" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E60" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C61" s="1">
         <v>2</v>
@@ -2060,116 +3447,3536 @@
       <c r="D61" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E61" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C62" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D62" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="E62" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C63" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D63" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E63" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C64" s="1">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="D64" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="E64" s="4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
         <v>133</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C65" s="1">
-        <v>118</v>
+        <v>72</v>
       </c>
       <c r="D65" s="1">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="E65" s="4">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="B66" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C66" s="1">
-        <v>72</v>
-      </c>
-      <c r="D66" s="1">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C67" s="11">
-        <f>SUM(C2:C66)</f>
-        <v>2936</v>
-      </c>
-      <c r="D67" s="11">
-        <f>SUM(D2:D66)</f>
-        <v>1831</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="C68" s="12" t="s">
+      <c r="C66" s="11">
+        <f>SUM(C2:C65)</f>
+        <v>2935</v>
+      </c>
+      <c r="D66" s="11">
+        <f>SUM(D2:D65)</f>
+        <v>1830</v>
+      </c>
+      <c r="E66" s="11">
+        <f>SUM(E2:E65)</f>
+        <v>2735</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="C67" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D67" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D68" s="12" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C69" s="12"/>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C70" s="11">
-        <f>SUM(C2:C64)</f>
-        <v>2746</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C71" s="12" t="s">
-        <v>130</v>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C68" s="12"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C69" s="11">
+        <f>SUM(C2:C63)</f>
+        <v>2745</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C70" s="12" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:C66">
-    <sortCondition ref="A1:A66"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:C65">
+    <sortCondition ref="A1:A65"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20F01D91-8B68-417A-BBFC-83C344345654}">
+  <dimension ref="A1:P201"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.28515625" customWidth="1"/>
+    <col min="11" max="11" width="10" style="22" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5703125" style="16" customWidth="1"/>
+    <col min="13" max="13" width="11" style="16" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.140625" style="16" customWidth="1"/>
+    <col min="15" max="15" width="14.140625" style="16" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="K1" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>396</v>
+      </c>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>397</v>
+      </c>
+      <c r="O3" s="16" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>398</v>
+      </c>
+      <c r="O4" s="16" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
+        <v>408</v>
+      </c>
+      <c r="O15" s="16" t="s">
+        <v>383</v>
+      </c>
+      <c r="P15" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" t="s">
+        <v>410</v>
+      </c>
+      <c r="O18" s="16" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>20</v>
+      </c>
+      <c r="B30" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B32" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>22</v>
+      </c>
+      <c r="B34" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>24</v>
+      </c>
+      <c r="B35" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>26</v>
+      </c>
+      <c r="B36" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>28</v>
+      </c>
+      <c r="B37" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>28</v>
+      </c>
+      <c r="B38" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>28</v>
+      </c>
+      <c r="B39" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>28</v>
+      </c>
+      <c r="B40" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>28</v>
+      </c>
+      <c r="B41" t="s">
+        <v>428</v>
+      </c>
+      <c r="O41" s="16" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>28</v>
+      </c>
+      <c r="B42" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>28</v>
+      </c>
+      <c r="B43" t="s">
+        <v>430</v>
+      </c>
+      <c r="O43" s="16" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>30</v>
+      </c>
+      <c r="B44" t="s">
+        <v>431</v>
+      </c>
+      <c r="O44" s="16" t="s">
+        <v>383</v>
+      </c>
+      <c r="P44" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>30</v>
+      </c>
+      <c r="B45" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>30</v>
+      </c>
+      <c r="B46" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>30</v>
+      </c>
+      <c r="B47" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>30</v>
+      </c>
+      <c r="B48" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>30</v>
+      </c>
+      <c r="B49" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>30</v>
+      </c>
+      <c r="B50" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>32</v>
+      </c>
+      <c r="B51" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>34</v>
+      </c>
+      <c r="B52" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>36</v>
+      </c>
+      <c r="B53" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>38</v>
+      </c>
+      <c r="B55" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>38</v>
+      </c>
+      <c r="B56" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>40</v>
+      </c>
+      <c r="B57" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>42</v>
+      </c>
+      <c r="B58" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>42</v>
+      </c>
+      <c r="B59" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>44</v>
+      </c>
+      <c r="B60" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>46</v>
+      </c>
+      <c r="B61" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>46</v>
+      </c>
+      <c r="B62" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>48</v>
+      </c>
+      <c r="B63" t="s">
+        <v>249</v>
+      </c>
+      <c r="O63" s="16" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>50</v>
+      </c>
+      <c r="B64" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>50</v>
+      </c>
+      <c r="B65" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>52</v>
+      </c>
+      <c r="B66" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>54</v>
+      </c>
+      <c r="B67" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>56</v>
+      </c>
+      <c r="B68" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>58</v>
+      </c>
+      <c r="B69" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>58</v>
+      </c>
+      <c r="B70" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>58</v>
+      </c>
+      <c r="B71" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>58</v>
+      </c>
+      <c r="B72" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>58</v>
+      </c>
+      <c r="B73" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>58</v>
+      </c>
+      <c r="B74" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>58</v>
+      </c>
+      <c r="B75" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>58</v>
+      </c>
+      <c r="B76" t="s">
+        <v>459</v>
+      </c>
+      <c r="O76" s="16" t="s">
+        <v>388</v>
+      </c>
+      <c r="P76" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>58</v>
+      </c>
+      <c r="B77" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>58</v>
+      </c>
+      <c r="B78" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>58</v>
+      </c>
+      <c r="B79" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>58</v>
+      </c>
+      <c r="B80" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>58</v>
+      </c>
+      <c r="B81" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>58</v>
+      </c>
+      <c r="B82" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>60</v>
+      </c>
+      <c r="B83" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>60</v>
+      </c>
+      <c r="B84" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>62</v>
+      </c>
+      <c r="B85" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>64</v>
+      </c>
+      <c r="B86" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>66</v>
+      </c>
+      <c r="B87" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>66</v>
+      </c>
+      <c r="B88" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>66</v>
+      </c>
+      <c r="B89" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>66</v>
+      </c>
+      <c r="B90" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>68</v>
+      </c>
+      <c r="B91" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>68</v>
+      </c>
+      <c r="B92" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>68</v>
+      </c>
+      <c r="B93" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>68</v>
+      </c>
+      <c r="B94" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>68</v>
+      </c>
+      <c r="B95" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>70</v>
+      </c>
+      <c r="B96" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>70</v>
+      </c>
+      <c r="B97" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>72</v>
+      </c>
+      <c r="B98" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>74</v>
+      </c>
+      <c r="B99" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>74</v>
+      </c>
+      <c r="B100" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>74</v>
+      </c>
+      <c r="B101" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>74</v>
+      </c>
+      <c r="B102" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>74</v>
+      </c>
+      <c r="B103" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>74</v>
+      </c>
+      <c r="B104" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>76</v>
+      </c>
+      <c r="B105" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>76</v>
+      </c>
+      <c r="B106" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>76</v>
+      </c>
+      <c r="B107" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>76</v>
+      </c>
+      <c r="B108" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>76</v>
+      </c>
+      <c r="B109" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>76</v>
+      </c>
+      <c r="B110" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>76</v>
+      </c>
+      <c r="B111" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>76</v>
+      </c>
+      <c r="B112" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>76</v>
+      </c>
+      <c r="B113" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>76</v>
+      </c>
+      <c r="B114" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>76</v>
+      </c>
+      <c r="B115" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>76</v>
+      </c>
+      <c r="B116" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>76</v>
+      </c>
+      <c r="B117" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>76</v>
+      </c>
+      <c r="B118" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>76</v>
+      </c>
+      <c r="B119" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>76</v>
+      </c>
+      <c r="B120" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>76</v>
+      </c>
+      <c r="B121" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>76</v>
+      </c>
+      <c r="B122" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>76</v>
+      </c>
+      <c r="B123" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>76</v>
+      </c>
+      <c r="B124" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>76</v>
+      </c>
+      <c r="B125" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>76</v>
+      </c>
+      <c r="B126" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>76</v>
+      </c>
+      <c r="B127" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>76</v>
+      </c>
+      <c r="B128" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>76</v>
+      </c>
+      <c r="B129" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>76</v>
+      </c>
+      <c r="B130" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>76</v>
+      </c>
+      <c r="B131" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>76</v>
+      </c>
+      <c r="B132" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>76</v>
+      </c>
+      <c r="B133" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>76</v>
+      </c>
+      <c r="B134" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>76</v>
+      </c>
+      <c r="B135" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>76</v>
+      </c>
+      <c r="B136" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>76</v>
+      </c>
+      <c r="B137" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>78</v>
+      </c>
+      <c r="B138" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>81</v>
+      </c>
+      <c r="B139" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>81</v>
+      </c>
+      <c r="B140" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>81</v>
+      </c>
+      <c r="B141" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>81</v>
+      </c>
+      <c r="B142" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>81</v>
+      </c>
+      <c r="B143" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>81</v>
+      </c>
+      <c r="B144" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>81</v>
+      </c>
+      <c r="B145" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>81</v>
+      </c>
+      <c r="B146" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>81</v>
+      </c>
+      <c r="B147" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>81</v>
+      </c>
+      <c r="B148" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>81</v>
+      </c>
+      <c r="B149" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>81</v>
+      </c>
+      <c r="B150" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>81</v>
+      </c>
+      <c r="B151" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>81</v>
+      </c>
+      <c r="B152" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>81</v>
+      </c>
+      <c r="B153" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>81</v>
+      </c>
+      <c r="B154" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>81</v>
+      </c>
+      <c r="B155" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>81</v>
+      </c>
+      <c r="B156" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>81</v>
+      </c>
+      <c r="B157" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>81</v>
+      </c>
+      <c r="B158" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>81</v>
+      </c>
+      <c r="B159" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>81</v>
+      </c>
+      <c r="B160" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>81</v>
+      </c>
+      <c r="B161" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>81</v>
+      </c>
+      <c r="B162" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>81</v>
+      </c>
+      <c r="B163" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>81</v>
+      </c>
+      <c r="B164" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>81</v>
+      </c>
+      <c r="B165" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>81</v>
+      </c>
+      <c r="B166" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>81</v>
+      </c>
+      <c r="B167" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>81</v>
+      </c>
+      <c r="B168" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>81</v>
+      </c>
+      <c r="B169" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>83</v>
+      </c>
+      <c r="B170" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>85</v>
+      </c>
+      <c r="B171" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>87</v>
+      </c>
+      <c r="B172" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>89</v>
+      </c>
+      <c r="B173" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>91</v>
+      </c>
+      <c r="B174" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>93</v>
+      </c>
+      <c r="B175" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>95</v>
+      </c>
+      <c r="B176" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>97</v>
+      </c>
+      <c r="B177" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>99</v>
+      </c>
+      <c r="B178" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>101</v>
+      </c>
+      <c r="B179" t="s">
+        <v>550</v>
+      </c>
+      <c r="O179" s="16" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>103</v>
+      </c>
+      <c r="B180" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>105</v>
+      </c>
+      <c r="B181" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>107</v>
+      </c>
+      <c r="B182" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>109</v>
+      </c>
+      <c r="B183" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>111</v>
+      </c>
+      <c r="B184" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>111</v>
+      </c>
+      <c r="B185" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>111</v>
+      </c>
+      <c r="B186" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>111</v>
+      </c>
+      <c r="B187" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>111</v>
+      </c>
+      <c r="B188" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>111</v>
+      </c>
+      <c r="B189" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>111</v>
+      </c>
+      <c r="B190" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>111</v>
+      </c>
+      <c r="B191" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>111</v>
+      </c>
+      <c r="B192" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>113</v>
+      </c>
+      <c r="B193" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>115</v>
+      </c>
+      <c r="B194" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>115</v>
+      </c>
+      <c r="B195" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>117</v>
+      </c>
+      <c r="B196" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>119</v>
+      </c>
+      <c r="B197" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>121</v>
+      </c>
+      <c r="B198" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>123</v>
+      </c>
+      <c r="B199" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>123</v>
+      </c>
+      <c r="B200" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>125</v>
+      </c>
+      <c r="B201" t="s">
+        <v>379</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F737F64-8981-4DA8-8BD9-86ED17E8287E}">
+  <dimension ref="A1:P202"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.5703125" customWidth="1"/>
+    <col min="11" max="11" width="10" style="16" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5703125" style="16" customWidth="1"/>
+    <col min="13" max="13" width="11" style="16" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.140625" style="16" customWidth="1"/>
+    <col min="15" max="15" width="14.140625" style="16" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>392</v>
+      </c>
+      <c r="K2" s="20" t="s">
+        <v>387</v>
+      </c>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>180</v>
+      </c>
+      <c r="K3" s="20" t="s">
+        <v>387</v>
+      </c>
+      <c r="O3" s="16" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>181</v>
+      </c>
+      <c r="K4" s="20" t="s">
+        <v>387</v>
+      </c>
+      <c r="O4" s="16" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
+        <v>192</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>385</v>
+      </c>
+      <c r="O15" s="16" t="s">
+        <v>383</v>
+      </c>
+      <c r="P15" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" t="s">
+        <v>195</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>394</v>
+      </c>
+      <c r="O18" s="16" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>10</v>
+      </c>
+      <c r="B27" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>18</v>
+      </c>
+      <c r="B33" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>20</v>
+      </c>
+      <c r="B35" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>22</v>
+      </c>
+      <c r="B37" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>22</v>
+      </c>
+      <c r="B38" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>22</v>
+      </c>
+      <c r="B39" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>22</v>
+      </c>
+      <c r="B40" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A41" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B41" t="s">
+        <v>218</v>
+      </c>
+      <c r="K41" s="20" t="s">
+        <v>387</v>
+      </c>
+      <c r="O41" s="16" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>26</v>
+      </c>
+      <c r="B42" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A43" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B43" t="s">
+        <v>220</v>
+      </c>
+      <c r="K43" s="19" t="s">
+        <v>387</v>
+      </c>
+      <c r="O43" s="16" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A44" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B44" t="s">
+        <v>221</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>385</v>
+      </c>
+      <c r="O44" s="16" t="s">
+        <v>383</v>
+      </c>
+      <c r="P44" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>28</v>
+      </c>
+      <c r="B45" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>28</v>
+      </c>
+      <c r="B46" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>28</v>
+      </c>
+      <c r="B47" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>28</v>
+      </c>
+      <c r="B48" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>28</v>
+      </c>
+      <c r="B49" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>28</v>
+      </c>
+      <c r="B50" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>28</v>
+      </c>
+      <c r="B51" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>28</v>
+      </c>
+      <c r="B52" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>28</v>
+      </c>
+      <c r="B53" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>28</v>
+      </c>
+      <c r="B54" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>28</v>
+      </c>
+      <c r="B55" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>28</v>
+      </c>
+      <c r="B56" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>28</v>
+      </c>
+      <c r="B57" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>30</v>
+      </c>
+      <c r="B58" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>30</v>
+      </c>
+      <c r="B59" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>30</v>
+      </c>
+      <c r="B60" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>32</v>
+      </c>
+      <c r="B61" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>32</v>
+      </c>
+      <c r="B62" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B63" t="s">
+        <v>240</v>
+      </c>
+      <c r="K63" s="19" t="s">
+        <v>387</v>
+      </c>
+      <c r="O63" s="16" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>36</v>
+      </c>
+      <c r="B64" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>38</v>
+      </c>
+      <c r="B65" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>38</v>
+      </c>
+      <c r="B66" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>38</v>
+      </c>
+      <c r="B67" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>40</v>
+      </c>
+      <c r="B68" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>42</v>
+      </c>
+      <c r="B69" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>44</v>
+      </c>
+      <c r="B70" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>46</v>
+      </c>
+      <c r="B71" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>48</v>
+      </c>
+      <c r="B72" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>50</v>
+      </c>
+      <c r="B73" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>52</v>
+      </c>
+      <c r="B74" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>52</v>
+      </c>
+      <c r="B75" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A76" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B76" t="s">
+        <v>253</v>
+      </c>
+      <c r="K76" s="16" t="s">
+        <v>385</v>
+      </c>
+      <c r="O76" s="16" t="s">
+        <v>388</v>
+      </c>
+      <c r="P76" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>56</v>
+      </c>
+      <c r="B77" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>58</v>
+      </c>
+      <c r="B78" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>58</v>
+      </c>
+      <c r="B79" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>58</v>
+      </c>
+      <c r="B80" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>58</v>
+      </c>
+      <c r="B81" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>58</v>
+      </c>
+      <c r="B82" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>58</v>
+      </c>
+      <c r="B83" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>58</v>
+      </c>
+      <c r="B84" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>58</v>
+      </c>
+      <c r="B85" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>58</v>
+      </c>
+      <c r="B86" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>58</v>
+      </c>
+      <c r="B87" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>58</v>
+      </c>
+      <c r="B88" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>58</v>
+      </c>
+      <c r="B89" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>58</v>
+      </c>
+      <c r="B90" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>58</v>
+      </c>
+      <c r="B91" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>58</v>
+      </c>
+      <c r="B92" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>60</v>
+      </c>
+      <c r="B93" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>62</v>
+      </c>
+      <c r="B94" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>62</v>
+      </c>
+      <c r="B95" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>64</v>
+      </c>
+      <c r="B96" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>66</v>
+      </c>
+      <c r="B97" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>66</v>
+      </c>
+      <c r="B98" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>66</v>
+      </c>
+      <c r="B99" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>68</v>
+      </c>
+      <c r="B100" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>68</v>
+      </c>
+      <c r="B101" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>68</v>
+      </c>
+      <c r="B102" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>68</v>
+      </c>
+      <c r="B103" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>68</v>
+      </c>
+      <c r="B104" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>68</v>
+      </c>
+      <c r="B105" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>68</v>
+      </c>
+      <c r="B106" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>68</v>
+      </c>
+      <c r="B107" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>70</v>
+      </c>
+      <c r="B108" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>72</v>
+      </c>
+      <c r="B109" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>74</v>
+      </c>
+      <c r="B110" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>74</v>
+      </c>
+      <c r="B111" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>74</v>
+      </c>
+      <c r="B112" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>74</v>
+      </c>
+      <c r="B113" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>74</v>
+      </c>
+      <c r="B114" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>76</v>
+      </c>
+      <c r="B115" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>76</v>
+      </c>
+      <c r="B116" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>76</v>
+      </c>
+      <c r="B117" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>76</v>
+      </c>
+      <c r="B118" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>76</v>
+      </c>
+      <c r="B119" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>76</v>
+      </c>
+      <c r="B120" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>76</v>
+      </c>
+      <c r="B121" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>76</v>
+      </c>
+      <c r="B122" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>76</v>
+      </c>
+      <c r="B123" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>76</v>
+      </c>
+      <c r="B124" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>76</v>
+      </c>
+      <c r="B125" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>76</v>
+      </c>
+      <c r="B126" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>76</v>
+      </c>
+      <c r="B127" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>76</v>
+      </c>
+      <c r="B128" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>76</v>
+      </c>
+      <c r="B129" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>76</v>
+      </c>
+      <c r="B130" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>76</v>
+      </c>
+      <c r="B131" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>76</v>
+      </c>
+      <c r="B132" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>76</v>
+      </c>
+      <c r="B133" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>76</v>
+      </c>
+      <c r="B134" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>76</v>
+      </c>
+      <c r="B135" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>76</v>
+      </c>
+      <c r="B136" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>76</v>
+      </c>
+      <c r="B137" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>76</v>
+      </c>
+      <c r="B138" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>78</v>
+      </c>
+      <c r="B139" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>80</v>
+      </c>
+      <c r="B140" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>81</v>
+      </c>
+      <c r="B141" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>81</v>
+      </c>
+      <c r="B142" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>81</v>
+      </c>
+      <c r="B143" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>81</v>
+      </c>
+      <c r="B144" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>81</v>
+      </c>
+      <c r="B145" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>81</v>
+      </c>
+      <c r="B146" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>81</v>
+      </c>
+      <c r="B147" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>81</v>
+      </c>
+      <c r="B148" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>81</v>
+      </c>
+      <c r="B149" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>81</v>
+      </c>
+      <c r="B150" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>81</v>
+      </c>
+      <c r="B151" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>81</v>
+      </c>
+      <c r="B152" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>81</v>
+      </c>
+      <c r="B153" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>81</v>
+      </c>
+      <c r="B154" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>81</v>
+      </c>
+      <c r="B155" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>81</v>
+      </c>
+      <c r="B156" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>81</v>
+      </c>
+      <c r="B157" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>81</v>
+      </c>
+      <c r="B158" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>81</v>
+      </c>
+      <c r="B159" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>81</v>
+      </c>
+      <c r="B160" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>81</v>
+      </c>
+      <c r="B161" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>81</v>
+      </c>
+      <c r="B162" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>81</v>
+      </c>
+      <c r="B163" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>81</v>
+      </c>
+      <c r="B164" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>81</v>
+      </c>
+      <c r="B165" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>81</v>
+      </c>
+      <c r="B166" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>81</v>
+      </c>
+      <c r="B167" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>83</v>
+      </c>
+      <c r="B168" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>85</v>
+      </c>
+      <c r="B169" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>87</v>
+      </c>
+      <c r="B170" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>89</v>
+      </c>
+      <c r="B171" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>91</v>
+      </c>
+      <c r="B172" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>91</v>
+      </c>
+      <c r="B173" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>91</v>
+      </c>
+      <c r="B174" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>93</v>
+      </c>
+      <c r="B175" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>95</v>
+      </c>
+      <c r="B176" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>97</v>
+      </c>
+      <c r="B177" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>99</v>
+      </c>
+      <c r="B178" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A179" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="B179" t="s">
+        <v>356</v>
+      </c>
+      <c r="K179" s="19" t="s">
+        <v>387</v>
+      </c>
+      <c r="O179" s="16" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>103</v>
+      </c>
+      <c r="B180" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>105</v>
+      </c>
+      <c r="B181" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>107</v>
+      </c>
+      <c r="B182" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>109</v>
+      </c>
+      <c r="B183" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>111</v>
+      </c>
+      <c r="B184" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>111</v>
+      </c>
+      <c r="B185" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>111</v>
+      </c>
+      <c r="B186" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>111</v>
+      </c>
+      <c r="B187" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>111</v>
+      </c>
+      <c r="B188" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>111</v>
+      </c>
+      <c r="B189" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>111</v>
+      </c>
+      <c r="B190" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>111</v>
+      </c>
+      <c r="B191" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>111</v>
+      </c>
+      <c r="B192" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>111</v>
+      </c>
+      <c r="B193" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>111</v>
+      </c>
+      <c r="B194" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>111</v>
+      </c>
+      <c r="B195" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>113</v>
+      </c>
+      <c r="B196" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>115</v>
+      </c>
+      <c r="B197" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>117</v>
+      </c>
+      <c r="B198" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>119</v>
+      </c>
+      <c r="B199" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>121</v>
+      </c>
+      <c r="B200" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>123</v>
+      </c>
+      <c r="B201" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>125</v>
+      </c>
+      <c r="B202" t="s">
+        <v>379</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>